--- a/data/trans_bre/LAWTONB_2R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 17,98</t>
+          <t>-14,35; 20,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 41,5</t>
+          <t>4,5; 42,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 37,27</t>
+          <t>-0,96; 35,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 22,64</t>
+          <t>-2,06; 24,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,59; 247,59</t>
+          <t>-65,92; 306,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 298,09</t>
+          <t>9,0; 295,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 301,63</t>
+          <t>-2,87; 316,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 108,02</t>
+          <t>-5,2; 118,56</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 12,66</t>
+          <t>-9,76; 11,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 25,36</t>
+          <t>-3,94; 24,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 26,02</t>
+          <t>4,16; 26,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 28,9</t>
+          <t>11,28; 28,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 235,45</t>
+          <t>-55,7; 200,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 213,98</t>
+          <t>-17,71; 196,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,21; 480,32</t>
+          <t>26,85; 488,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,62; 419,15</t>
+          <t>55,51; 407,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 23,26</t>
+          <t>-1,3; 23,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 14,58</t>
+          <t>-15,4; 15,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 10,88</t>
+          <t>-11,61; 10,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 18,3</t>
+          <t>-2,02; 20,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 684,21</t>
+          <t>-17,5; 722,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,6; 97,85</t>
+          <t>-46,96; 99,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-69,39; 146,55</t>
+          <t>-70,69; 140,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 100,44</t>
+          <t>-6,87; 118,04</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 29,86</t>
+          <t>5,41; 28,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 15,52</t>
+          <t>-13,74; 15,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 14,6</t>
+          <t>-11,42; 12,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 11,93</t>
+          <t>-5,29; 13,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,06; 1521,86</t>
+          <t>25,14; 1281,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 89,0</t>
+          <t>-43,18; 87,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,58; 126,5</t>
+          <t>-49,44; 100,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 85,93</t>
+          <t>-21,07; 107,56</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 22,91</t>
+          <t>-18,09; 23,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 27,29</t>
+          <t>-13,03; 26,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,58; 45,01</t>
+          <t>10,4; 43,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 13,98</t>
+          <t>-9,56; 14,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 135,13</t>
+          <t>-47,53; 161,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,25; 251,15</t>
+          <t>-39,9; 303,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,54; 1162,36</t>
+          <t>46,27; 1052,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 94,37</t>
+          <t>-32,1; 108,39</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 11,76</t>
+          <t>-14,1; 13,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 14,51</t>
+          <t>-19,06; 13,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 21,52</t>
+          <t>-11,16; 21,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 16,33</t>
+          <t>-4,51; 16,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,77; 113,3</t>
+          <t>-56,98; 132,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,13; 78,8</t>
+          <t>-50,44; 71,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 130,71</t>
+          <t>-37,77; 123,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 63,67</t>
+          <t>-11,71; 65,79</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 12,45</t>
+          <t>-3,87; 12,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 10,82</t>
+          <t>-9,78; 12,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 21,67</t>
+          <t>0,43; 20,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 19,43</t>
+          <t>-12,06; 19,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 251,42</t>
+          <t>-35,79; 269,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,16; 66,66</t>
+          <t>-34,5; 76,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 170,96</t>
+          <t>1,84; 175,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-80,05; 227,71</t>
+          <t>-81,59; 217,47</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 13,88</t>
+          <t>-4,93; 13,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 15,73</t>
+          <t>-3,01; 14,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 12,28</t>
+          <t>-5,19; 12,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,59; 20,04</t>
+          <t>8,17; 20,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 114,26</t>
+          <t>-23,57; 120,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 253,67</t>
+          <t>-20,1; 242,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 137,87</t>
+          <t>-32,36; 139,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>74,88; 346,81</t>
+          <t>75,4; 395,88</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,62</t>
+          <t>1,36; 9,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 10,99</t>
+          <t>0,31; 10,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 13,05</t>
+          <t>4,51; 13,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 12,72</t>
+          <t>-5,61; 12,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,9; 91,11</t>
+          <t>9,57; 89,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 60,66</t>
+          <t>1,15; 61,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,81; 101,07</t>
+          <t>26,84; 103,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 80,65</t>
+          <t>-30,86; 80,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/LAWTONB_2R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,85</t>
+          <t>11,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 20,15</t>
+          <t>-14,27; 19,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 42,18</t>
+          <t>2,39; 41,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 35,84</t>
+          <t>-1,45; 38,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 24,21</t>
+          <t>-0,29; 25,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 306,23</t>
+          <t>-68,57; 258,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,0; 295,44</t>
+          <t>3,12; 272,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 316,76</t>
+          <t>-10,51; 291,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 118,56</t>
+          <t>-1,4; 130,25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,56</t>
+          <t>21,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>171,09%</t>
+          <t>181,59%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 11,76</t>
+          <t>-8,31; 12,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 24,82</t>
+          <t>-2,88; 26,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 26,69</t>
+          <t>5,43; 27,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,28; 28,89</t>
+          <t>11,95; 29,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,7; 200,66</t>
+          <t>-53,43; 215,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 196,3</t>
+          <t>-12,7; 211,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,85; 488,56</t>
+          <t>32,71; 541,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,51; 407,72</t>
+          <t>58,93; 451,83</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>9,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 23,36</t>
+          <t>-1,97; 22,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 15,19</t>
+          <t>-16,55; 14,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 10,52</t>
+          <t>-11,67; 9,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 20,26</t>
+          <t>-0,88; 19,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 722,27</t>
+          <t>-25,67; 489,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 99,39</t>
+          <t>-50,52; 91,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,69; 140,1</t>
+          <t>-66,02; 145,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 118,04</t>
+          <t>-3,32; 106,46</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 28,91</t>
+          <t>5,53; 28,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 15,12</t>
+          <t>-13,15; 16,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 12,84</t>
+          <t>-13,27; 13,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 13,02</t>
+          <t>-4,66; 12,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,14; 1281,59</t>
+          <t>26,97; 1410,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 87,55</t>
+          <t>-39,14; 103,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 100,97</t>
+          <t>-54,13; 113,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 107,56</t>
+          <t>-20,98; 101,89</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 23,02</t>
+          <t>-15,81; 24,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 26,3</t>
+          <t>-12,84; 25,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,4; 43,89</t>
+          <t>9,23; 43,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 14,09</t>
+          <t>-8,14; 14,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 161,45</t>
+          <t>-46,18; 174,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 303,22</t>
+          <t>-43,59; 309,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,27; 1052,93</t>
+          <t>40,1; 941,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 108,39</t>
+          <t>-29,05; 108,77</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 13,19</t>
+          <t>-16,96; 12,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 13,73</t>
+          <t>-17,96; 14,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 21,6</t>
+          <t>-11,0; 21,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 16,69</t>
+          <t>-5,67; 16,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 132,82</t>
+          <t>-61,93; 136,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 71,57</t>
+          <t>-49,1; 76,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 123,3</t>
+          <t>-37,49; 142,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 65,79</t>
+          <t>-15,39; 65,48</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>17,28</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>178,16%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 12,35</t>
+          <t>-2,84; 12,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 12,34</t>
+          <t>-10,18; 11,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 20,7</t>
+          <t>0,9; 21,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 19,09</t>
+          <t>9,81; 25,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 269,72</t>
+          <t>-29,44; 264,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 76,23</t>
+          <t>-35,75; 75,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 175,45</t>
+          <t>3,65; 183,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-81,59; 217,47</t>
+          <t>69,25; 409,63</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,47</t>
+          <t>14,71</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>184,84%</t>
+          <t>178,88%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 13,45</t>
+          <t>-6,24; 13,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 14,8</t>
+          <t>-3,02; 15,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 12,58</t>
+          <t>-4,82; 12,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 20,02</t>
+          <t>8,98; 20,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 120,21</t>
+          <t>-28,98; 120,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 242,85</t>
+          <t>-21,77; 259,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 139,39</t>
+          <t>-30,72; 158,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>75,4; 395,88</t>
+          <t>77,64; 383,59</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>12,45</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 9,7</t>
+          <t>1,27; 9,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 10,92</t>
+          <t>0,54; 10,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 13,28</t>
+          <t>4,1; 13,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 12,89</t>
+          <t>9,19; 15,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,57; 89,44</t>
+          <t>6,46; 91,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 61,16</t>
+          <t>2,4; 57,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,84; 103,38</t>
+          <t>23,98; 99,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 80,78</t>
+          <t>49,22; 111,34</t>
         </is>
       </c>
     </row>
